--- a/artfynd/A 58427-2025 artfynd.xlsx
+++ b/artfynd/A 58427-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129917549</v>
       </c>
       <c r="B2" t="n">
-        <v>98790</v>
+        <v>98794</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -802,7 +802,7 @@
         <v>129917656</v>
       </c>
       <c r="B3" t="n">
-        <v>98790</v>
+        <v>98794</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -927,7 +927,7 @@
         <v>129917484</v>
       </c>
       <c r="B4" t="n">
-        <v>98790</v>
+        <v>98794</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 58427-2025 artfynd.xlsx
+++ b/artfynd/A 58427-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129917549</v>
       </c>
       <c r="B2" t="n">
-        <v>98794</v>
+        <v>98797</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -802,7 +802,7 @@
         <v>129917656</v>
       </c>
       <c r="B3" t="n">
-        <v>98794</v>
+        <v>98797</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -927,7 +927,7 @@
         <v>129917484</v>
       </c>
       <c r="B4" t="n">
-        <v>98794</v>
+        <v>98797</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 58427-2025 artfynd.xlsx
+++ b/artfynd/A 58427-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129917549</v>
       </c>
       <c r="B2" t="n">
-        <v>98797</v>
+        <v>98798</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -802,7 +802,7 @@
         <v>129917656</v>
       </c>
       <c r="B3" t="n">
-        <v>98797</v>
+        <v>98798</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -927,7 +927,7 @@
         <v>129917484</v>
       </c>
       <c r="B4" t="n">
-        <v>98797</v>
+        <v>98798</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 58427-2025 artfynd.xlsx
+++ b/artfynd/A 58427-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129917549</v>
       </c>
       <c r="B2" t="n">
-        <v>98798</v>
+        <v>98815</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -802,7 +802,7 @@
         <v>129917656</v>
       </c>
       <c r="B3" t="n">
-        <v>98798</v>
+        <v>98815</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -927,7 +927,7 @@
         <v>129917484</v>
       </c>
       <c r="B4" t="n">
-        <v>98798</v>
+        <v>98815</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 58427-2025 artfynd.xlsx
+++ b/artfynd/A 58427-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129917549</v>
       </c>
       <c r="B2" t="n">
-        <v>98831</v>
+        <v>98833</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -802,7 +802,7 @@
         <v>129917656</v>
       </c>
       <c r="B3" t="n">
-        <v>98831</v>
+        <v>98833</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -927,7 +927,7 @@
         <v>129917484</v>
       </c>
       <c r="B4" t="n">
-        <v>98831</v>
+        <v>98833</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 58427-2025 artfynd.xlsx
+++ b/artfynd/A 58427-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129917549</v>
       </c>
       <c r="B2" t="n">
-        <v>98833</v>
+        <v>98920</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -802,7 +802,7 @@
         <v>129917656</v>
       </c>
       <c r="B3" t="n">
-        <v>98833</v>
+        <v>98920</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -927,7 +927,7 @@
         <v>129917484</v>
       </c>
       <c r="B4" t="n">
-        <v>98833</v>
+        <v>98920</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 58427-2025 artfynd.xlsx
+++ b/artfynd/A 58427-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129917549</v>
       </c>
       <c r="B2" t="n">
-        <v>98920</v>
+        <v>98833</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -802,7 +802,7 @@
         <v>129917656</v>
       </c>
       <c r="B3" t="n">
-        <v>98920</v>
+        <v>98833</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -927,7 +927,7 @@
         <v>129917484</v>
       </c>
       <c r="B4" t="n">
-        <v>98920</v>
+        <v>98833</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 58427-2025 artfynd.xlsx
+++ b/artfynd/A 58427-2025 artfynd.xlsx
@@ -1051,7 +1051,7 @@
         <v>130453447</v>
       </c>
       <c r="B5" t="n">
-        <v>57826</v>
+        <v>57852</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1171,7 +1171,7 @@
         <v>130351461</v>
       </c>
       <c r="B6" t="n">
-        <v>57016</v>
+        <v>57042</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 58427-2025 artfynd.xlsx
+++ b/artfynd/A 58427-2025 artfynd.xlsx
@@ -1051,7 +1051,7 @@
         <v>130453447</v>
       </c>
       <c r="B5" t="n">
-        <v>57852</v>
+        <v>57854</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1171,7 +1171,7 @@
         <v>130351461</v>
       </c>
       <c r="B6" t="n">
-        <v>57042</v>
+        <v>57044</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 58427-2025 artfynd.xlsx
+++ b/artfynd/A 58427-2025 artfynd.xlsx
@@ -1051,7 +1051,7 @@
         <v>130453447</v>
       </c>
       <c r="B5" t="n">
-        <v>57854</v>
+        <v>57862</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1171,7 +1171,7 @@
         <v>130351461</v>
       </c>
       <c r="B6" t="n">
-        <v>57044</v>
+        <v>57052</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 58427-2025 artfynd.xlsx
+++ b/artfynd/A 58427-2025 artfynd.xlsx
@@ -1051,7 +1051,7 @@
         <v>130453447</v>
       </c>
       <c r="B5" t="n">
-        <v>57862</v>
+        <v>57863</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1171,7 +1171,7 @@
         <v>130351461</v>
       </c>
       <c r="B6" t="n">
-        <v>57052</v>
+        <v>57053</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 58427-2025 artfynd.xlsx
+++ b/artfynd/A 58427-2025 artfynd.xlsx
@@ -1051,7 +1051,7 @@
         <v>130453447</v>
       </c>
       <c r="B5" t="n">
-        <v>57863</v>
+        <v>57864</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 58427-2025 artfynd.xlsx
+++ b/artfynd/A 58427-2025 artfynd.xlsx
@@ -675,46 +675,38 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129917549</v>
+        <v>130453447</v>
       </c>
       <c r="B2" t="n">
-        <v>98920</v>
+        <v>57953</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr"/>
       <c r="N2" t="inlineStr">
         <is>
           <t>observerad</t>
@@ -729,7 +721,7 @@
         <v>500446</v>
       </c>
       <c r="R2" t="n">
-        <v>6712635</v>
+        <v>6712569</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -774,13 +766,17 @@
           <t>15:00</t>
         </is>
       </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Spår av tretåig hackspett på tall.</t>
+        </is>
+      </c>
       <c r="AD2" t="b">
         <v>0</v>
       </c>
       <c r="AE2" t="b">
         <v>0</v>
       </c>
-      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -799,60 +795,56 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129917656</v>
+        <v>130351461</v>
       </c>
       <c r="B3" t="n">
-        <v>98920</v>
+        <v>57141</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>100138</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>80</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>m²</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Väster om myggtjärn, Dlr</t>
+          <t>Dånbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>500461</v>
+        <v>500420</v>
       </c>
       <c r="R3" t="n">
-        <v>6712593</v>
+        <v>6712586</v>
       </c>
       <c r="S3" t="n">
-        <v>40</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -891,12 +883,12 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Ungefärlig storlek på yta där det finns rikligt med fynd av knärot.</t>
+          <t>Tydliga fynd av gammal spelspillning, vitaktiga i ena änden, under tre tallar.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -905,19 +897,18 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Signe Rönnegård</t>
+          <t>Ann-Sofie Rönnegård</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Signe Rönnegård</t>
+          <t>Ann-Sofie Rönnegård</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
@@ -927,7 +918,7 @@
         <v>129917484</v>
       </c>
       <c r="B4" t="n">
-        <v>98920</v>
+        <v>99118</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1048,38 +1039,46 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>130453447</v>
+        <v>129917549</v>
       </c>
       <c r="B5" t="n">
-        <v>57878</v>
+        <v>99118</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr"/>
       <c r="N5" t="inlineStr">
         <is>
           <t>observerad</t>
@@ -1094,7 +1093,7 @@
         <v>500446</v>
       </c>
       <c r="R5" t="n">
-        <v>6712569</v>
+        <v>6712635</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1139,17 +1138,13 @@
           <t>15:00</t>
         </is>
       </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Spår av tretåig hackspett på tall.</t>
-        </is>
-      </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1168,56 +1163,60 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>130351461</v>
+        <v>129917656</v>
       </c>
       <c r="B6" t="n">
-        <v>57067</v>
+        <v>99118</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100138</v>
+        <v>220787</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>80</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>m²</t>
         </is>
       </c>
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Dånbäcken, Dlr</t>
+          <t>Väster om myggtjärn, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>500420</v>
+        <v>500461</v>
       </c>
       <c r="R6" t="n">
-        <v>6712586</v>
+        <v>6712593</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>40</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1256,12 +1255,12 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Tydliga fynd av gammal spelspillning, vitaktiga i ena änden, under tre tallar.</t>
+          <t>Ungefärlig storlek på yta där det finns rikligt med fynd av knärot.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1270,18 +1269,19 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Ann-Sofie Rönnegård</t>
+          <t>Signe Rönnegård</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Ann-Sofie Rönnegård</t>
+          <t>Signe Rönnegård</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>

--- a/artfynd/A 58427-2025 artfynd.xlsx
+++ b/artfynd/A 58427-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY6"/>
+  <dimension ref="A1:AZ6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -670,6 +670,11 @@
       <c r="AY1" t="inlineStr">
         <is>
           <t>Projektnamn</t>
+        </is>
+      </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
         </is>
       </c>
     </row>
@@ -792,6 +797,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130453447</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -912,6 +922,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130351461</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1036,6 +1051,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129917484</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1160,6 +1180,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129917549</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1285,8 +1310,20 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129917656</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>